--- a/r4-ELGA-IV-Herzinsuffizienz-fokuswoche/StructureDefinition-iv-careplan-schulung.xlsx
+++ b/r4-ELGA-IV-Herzinsuffizienz-fokuswoche/StructureDefinition-iv-careplan-schulung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-23T11:55:38+00:00</t>
+    <t>2025-01-29T11:32:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
